--- a/reference-docs/SOURCE_OF_TRUTH_Super Mega Baseball 4 Rosters.xlsx
+++ b/reference-docs/SOURCE_OF_TRUTH_Super Mega Baseball 4 Rosters.xlsx
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B14" s="117" t="inlineStr">
         <is>
-          <t>Seymour Scoks</t>
+          <t>Seymour Socks</t>
         </is>
       </c>
       <c r="C14" s="117" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B15" s="123" t="inlineStr">
         <is>
-          <t>Lars Stadkeleef</t>
+          <t>Lars Stadkleef</t>
         </is>
       </c>
       <c r="C15" s="123" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="B11" s="259" t="inlineStr">
         <is>
-          <t>Pex Flext</t>
+          <t>Pex Flexi</t>
         </is>
       </c>
       <c r="C11" s="259" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Dano Yoshida</t>
+          <t>Danno Yoshida</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
